--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-09-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,4 +417,3423 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>I4L</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>B4L</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BSO</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Superstore</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Materials Market</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Trade Insulations</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Wholesale</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Hub</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>InsulationUK</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Online Insulation Sales</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Online</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Planet Insulation</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Shop</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Building Materials Direct</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Insulation Bee</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>DIY Building supplies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>25mm Celotex</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25mm Celotex TB4025 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £10.50</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>£10.50</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>£10.50</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>£10.50</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>£10.68</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>£10.50</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>£10.55</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>£11.54</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>£10.65</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>£10.52</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>£20.73</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>£16.68</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>£20.56</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>£10.95 Pre Sale Price-£11.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30mm Celotex</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30mm Celotex TB4030 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £12.30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>£12.30</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>£12.30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>£12.30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>£12.05</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>£12.25</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>£11.88</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>£12.83</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>£12.33</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>£11.77</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>£12.29</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>£23.92</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>£19.42</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>£12.30 Pre Sale Price-£13.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>40mm Celotex</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>40mm Celotex TB4040 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £15.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>£15.50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>£15.50</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£15.50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>£15.39</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>£15.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>£15.38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>£15.75</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>£15.28</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>£14.93</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>£22.68</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>£31.22</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>£15.75 Pre Sale Price-£17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>50mm Celotex</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50mm Celotex GA4050 2.4m x 1.2m </t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £16.00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£15.67</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>£15.65</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>£15.60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>£16.75</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>£15.91</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>£15.59</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>£17.14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>£30.19</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>£21.93</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>£16.50 Pre Sale Price-£19.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>60mm Celotex</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>60mm Celotex GA4060 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £20.25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£20.25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£20.25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£20.25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>£19.85</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>£19.99</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£20.00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>£21.46</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>£20.60</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>£19.99</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>£20.47</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>£35.91</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>£34.64</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>£20.59 Pre Sale Price-£21.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>70mm Celotex</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>70mm Celotex GA4070 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £22.50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>£22.50</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>£22.50</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>£22.50</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>£21.79</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>£21.99</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>£21.75</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>£23.15</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>£22.24</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>£21.58</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>£22.34</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>£43.61</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>£34.85</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>£37.49</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>£22.76 Pre Sale Price-£24.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>75mm Celotex</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>75mm Celotex GA4075 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £22.54</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>£22.54</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>£22.54</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>£23.50</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>£22.54</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>£22.53</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>£22.02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>£23.50</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>£22.57</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>£21.90</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>£22.52</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>£45.09</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>£34.66</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>£39.47</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>£23.50 Pre Sale Price-£25.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>80mm Celotex</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>80mm Celotex GA4080 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £25.75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>£25.75</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>£25.75</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>£25.75</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>£25.27</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>£25.26</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>£25.25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>£26.79</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>£25.79</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>£25.02</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>£24.64</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>£48.08</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>£38.36</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>£43.23</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>£25.79 Pre Sale Price-£27.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>90mm Celotex</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>90mm Celotex GA4090 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £28.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>£28.00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>£27.34</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>£27.33</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>£27.33</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>£29.33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>£27.95</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>£27.12</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>£27.5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>£53.13</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>£41.16</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>£52.15</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>£28.80 Pre Sale Price-£31.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>100mm Celotex</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>100mm Celotex GA4100 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £27.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>£27.00</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£27.00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£27.00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>£27.39</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>£26.99</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>£26.88</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>£27.29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>£26.87</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>£26.64</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>£28.71</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>£54.41</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>£38.47</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>£49.32</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>£27.38 Pre Sale Price-£32.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>110mm Celotex</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>110mm Celotex XR4110 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £36.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>£35.57</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>£35.56</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>£35.88</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>£41.79</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>£36.31</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>£32.97</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>£50.96</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>£36.30 Pre Sale Price-£39.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>120mm Celotex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>120mm Celotex XR4120 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £34.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>£34.50</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>£34.50</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>£34.50</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>£34.10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>£33.70</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>£33.00</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>£35.08</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>£33.72</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>£32.72</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>£34.0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>£66.89</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>£51.70</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>£34.90 Pre Sale Price-£37.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>130mm Celotex</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130mm Celotex XR4130 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £41.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>£41.00</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>£41.00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>£41.00</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>£40.27</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>£40.25</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>£40.24</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>£46.74</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>£41.10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>£39.88</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>£38.6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>£73.80</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>£61.93</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>£717.24</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>£41.09 Pre Sale Price-£44.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>140mm Celotex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>140mm Celotex XR4140 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>£41.06</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>£41.05</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>£41.04</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>£41.93</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>£40.68</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>£43.83</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>£78.85</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>£65.16</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>£717.6</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>150mm Celotex</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>150mm Celotex XR4150 2.4m X 1.2m</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £41.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>£41.50</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>£40.96</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>£40.95</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>£41.00</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>£43.58</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>£41.86</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>£40.62</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>£42.21</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>£82.06</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>£74.88</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>£43.50 Pre Sale Price-£49.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>165mm Celotex1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>165mm Celotex XR4165 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £695.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>£695.00</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>£877.92</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>£719.88</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>£768.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>£857.88</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>£695.52</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>£653.19</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>£959.7</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>POA or OOS</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>xr4200pal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200mm Celotex XR4200 2.4m x 1.2m </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Regular price
+                  £895.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>£895.00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>£960.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>£935.88</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>£984.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>£1029.48</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>£1407.24</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>£873.16</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>£861.09</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>£1164.06</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>£1073.28</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>£962.37 Pre Sale Price-£1,040.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PL4025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Celotex PL4025 37.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>£35.00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>£29.80</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>£29.50</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>£32.00</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>£37.39</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>£29.82</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>£28.70</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>£36.95</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>£68.31</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>£48.24</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>£49.22</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>£37.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PL4040</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Celotex PL4040 52.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>£43.00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>£36.00</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>£35.90</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>£36.36</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>£47.29</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>£36.74</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>£34.65</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>£44.24</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>£79.12</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>£58.53</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>£49.55</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>£45.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PL4050</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Celotex PL4050 62.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>£47.00</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>£39.15</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>£42.00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>£49.49</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>£40.21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>£37.62</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>£52.32</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>£87.37</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>£66.08</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>£68.97</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>£50.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PL4060</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Celotex PL4060 72.5mm x 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>£54.00</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>£43.62</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>£46.88</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>£54.99</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>£44.52</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>£42.88</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>£55.49</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>£92.82</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>£68.87</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>£79.88</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>£55.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>celcav50</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 50mm </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>£43.80</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>£43.80</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>£43.80</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>£58.51</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>£43.99</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>£43.63</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>£78.54</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>£43.55</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>£41.25</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>£68.43</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>£65.48</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>£60.57</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>£44.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cw40755</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 75mm </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>£43.90</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>£43.90</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>£43.90</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>£44.00</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>£53.49</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>£43.90</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>£43.63</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>£85.44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>£47.03</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>£39.38</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>£71.62</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>£63.59</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>£68.48</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>£49.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>celcav85</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Celotex CW 85mm (16 Packs)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>£992.06</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>£992.06</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>£992.06</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>£992.06</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>£1439.04</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>£1787.2</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cw4100</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Celotex CW 100mm </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>£43.75</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>£45.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>£55.89</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>£43.99</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>£44.38</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>£81.9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>£43.14</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+	GetHandleVerifier [0x0x7ff6470330f5+79493]
+	GetHandleVerifier [0x0x7ff647033150+79584]
+	(No symbol) [0x0x7ff646db01ba]
+	(No symbol) [0x0x7ff646e08067]
+	(No symbol) [0x0x7ff646e0832c]
+	(No symbol) [0x0x7ff646e5be27]
+	(No symbol) [0x0x7ff646e3074f]
+	(No symbol) [0x0x7ff646e58b8b]
+	(No symbol) [0x0x7ff646e304e3]
+	(No symbol) [0x0x7ff646df8e92]
+	(No symbol) [0x0x7ff646df9c63]
+	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
+	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
+	GetHandleVerifier [0x0x7ff64730b357+3061991]
+	GetHandleVerifier [0x0x7ff64704d60e+187294]
+	GetHandleVerifier [0x0x7ff64705557f+219919]
+	GetHandleVerifier [0x0x7ff64703c294+116772]
+	GetHandleVerifier [0x0x7ff64703c449+117209]
+	GetHandleVerifier [0x0x7ff647022618+11176]
+	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
+	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
+</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>£40.53</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>£72.21</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>£62.02</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>£67.41</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>£47.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CELOTC1090</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Celotex Thermaclass Cavity Wall 21 90mm x 1.19m x 0.45m (96 Sh / 51.40m2)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>£1,150.00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>£1,150.00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>£1,150.00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>£1,200.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>£1160.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>£1152.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>£1248.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>£1172.16</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>£1129.12</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>£1057.71</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>£1948.16</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>£1588.8</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>£1186.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CELOTC1115</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Celotex Thermaclass Cavity Wall 21 115mm x 1.19m x 0.45m (80 Sh / 42.84m2)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>£1,250.00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>£1,250.00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>£1,250.00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>£1,250.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>£1296.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>£1280.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>£1328.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>£1407.2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>£1254.56</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>£1126.15</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>£2157.92</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>£1700.0</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>£1286.72</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CELOTC1140</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Celotex Thermaclass Cavity Wall 21 140mm x 1.19m x 0.45m (64 Sh / 34.27m2)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>£1,225.00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>£1,225.00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>£1,213.28</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>£1,225.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>£1280.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>£1280.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>£1336.96</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>£1189.12</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>£1096.66</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>£1804.16</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>£1314.88</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_22-09-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£11.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -905,17 +905,17 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Regular price
-                  £16.00</t>
+                  £15.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£16.00</t>
+          <t>£15.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£16.00</t>
+          <t>£15.60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £22.54</t>
+                  £22.02</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£22.54</t>
+          <t>£22.02</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£22.54</t>
+          <t>£22.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £27.00</t>
+                  £26.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£27.00</t>
+          <t>£26.88</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£27.00</t>
+          <t>£26.88</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2246,17 +2246,17 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Regular price
-                  £41.50</t>
+                  £40.95</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£41.50</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.185); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6470330f5+79493]
-	GetHandleVerifier [0x0x7ff647033150+79584]
-	(No symbol) [0x0x7ff646db01ba]
-	(No symbol) [0x0x7ff646e08067]
-	(No symbol) [0x0x7ff646e0832c]
-	(No symbol) [0x0x7ff646e5be27]
-	(No symbol) [0x0x7ff646e3074f]
-	(No symbol) [0x0x7ff646e58b8b]
-	(No symbol) [0x0x7ff646e304e3]
-	(No symbol) [0x0x7ff646df8e92]
-	(No symbol) [0x0x7ff646df9c63]
-	GetHandleVerifier [0x0x7ff6472f0dbd+2954061]
-	GetHandleVerifier [0x0x7ff6472eb02a+2930106]
-	GetHandleVerifier [0x0x7ff64730b357+3061991]
-	GetHandleVerifier [0x0x7ff64704d60e+187294]
-	GetHandleVerifier [0x0x7ff64705557f+219919]
-	GetHandleVerifier [0x0x7ff64703c294+116772]
-	GetHandleVerifier [0x0x7ff64703c449+117209]
-	GetHandleVerifier [0x0x7ff647022618+11176]
+	GetHandleVerifier [0x0x7ff7a66f30f5+79493]
+	GetHandleVerifier [0x0x7ff7a66f3150+79584]
+	(No symbol) [0x0x7ff7a64701ba]
+	(No symbol) [0x0x7ff7a64c8067]
+	(No symbol) [0x0x7ff7a64c832c]
+	(No symbol) [0x0x7ff7a651be27]
+	(No symbol) [0x0x7ff7a64f074f]
+	(No symbol) [0x0x7ff7a6518b8b]
+	(No symbol) [0x0x7ff7a64f04e3]
+	(No symbol) [0x0x7ff7a64b8e92]
+	(No symbol) [0x0x7ff7a64b9c63]
+	GetHandleVerifier [0x0x7ff7a69b0dbd+2954061]
+	GetHandleVerifier [0x0x7ff7a69ab02a+2930106]
+	GetHandleVerifier [0x0x7ff7a69cb357+3061991]
+	GetHandleVerifier [0x0x7ff7a670d60e+187294]
+	GetHandleVerifier [0x0x7ff7a671557f+219919]
+	GetHandleVerifier [0x0x7ff7a66fc294+116772]
+	GetHandleVerifier [0x0x7ff7a66fc449+117209]
+	GetHandleVerifier [0x0x7ff7a66e2618+11176]
 	BaseThreadInitThunk [0x0x7ff81809e8d7+23]
 	RtlUserThreadStart [0x0x7ff8189e8d9c+44]
 </t>
